--- a/base_slips_nfs.xlsx
+++ b/base_slips_nfs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafae\Downloads\projeto consulta NF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3DDC02-2AE8-4461-9652-408C4DDBECF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD5A517-819F-4904-8015-57E96F17EFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
     <t>Data da atualização</t>
   </si>
   <si>
-    <t>001</t>
+    <t>CDV01</t>
   </si>
   <si>
     <t>Supermercado Alvorada Ltda</t>
@@ -76,7 +76,7 @@
     <t>2026-10-01</t>
   </si>
   <si>
-    <t>002</t>
+    <t>CDV02</t>
   </si>
   <si>
     <t>Comercial São José</t>
@@ -100,7 +100,7 @@
     <t>2026-10-02</t>
   </si>
   <si>
-    <t>003</t>
+    <t>CDV03</t>
   </si>
   <si>
     <t>Distribuidora Central</t>
@@ -124,7 +124,7 @@
     <t>2026-10-03</t>
   </si>
   <si>
-    <t>004</t>
+    <t>CDV04</t>
   </si>
   <si>
     <t>Mercado Bom Preço</t>
@@ -148,7 +148,7 @@
     <t>2026-10-04</t>
   </si>
   <si>
-    <t>005</t>
+    <t>CDV05</t>
   </si>
   <si>
     <t>Atacado Boa Vista</t>
@@ -169,7 +169,7 @@
     <t>2026-10-05</t>
   </si>
   <si>
-    <t>006</t>
+    <t>CDV06</t>
   </si>
   <si>
     <t>10006</t>
@@ -184,7 +184,7 @@
     <t>2026-10-06</t>
   </si>
   <si>
-    <t>007</t>
+    <t>CDV07</t>
   </si>
   <si>
     <t>10007</t>
@@ -196,7 +196,7 @@
     <t>2026-09-07</t>
   </si>
   <si>
-    <t>008</t>
+    <t>CDV08</t>
   </si>
   <si>
     <t>10008</t>
@@ -208,7 +208,7 @@
     <t>2026-09-08</t>
   </si>
   <si>
-    <t>009</t>
+    <t>CDV09</t>
   </si>
   <si>
     <t>10009</t>
@@ -220,7 +220,7 @@
     <t>2026-09-09</t>
   </si>
   <si>
-    <t>010</t>
+    <t>CDV10</t>
   </si>
   <si>
     <t>10010</t>
@@ -232,7 +232,7 @@
     <t>2026-09-10</t>
   </si>
   <si>
-    <t>011</t>
+    <t>CDV11</t>
   </si>
   <si>
     <t>10011</t>
@@ -244,7 +244,7 @@
     <t>2026-09-11</t>
   </si>
   <si>
-    <t>012</t>
+    <t>CDV12</t>
   </si>
   <si>
     <t>10012</t>
@@ -256,7 +256,7 @@
     <t>2026-09-12</t>
   </si>
   <si>
-    <t>013</t>
+    <t>CDV13</t>
   </si>
   <si>
     <t>10013</t>
@@ -268,7 +268,7 @@
     <t>2026-09-13</t>
   </si>
   <si>
-    <t>014</t>
+    <t>CDV14</t>
   </si>
   <si>
     <t>10014</t>
@@ -280,7 +280,7 @@
     <t>2026-09-14</t>
   </si>
   <si>
-    <t>015</t>
+    <t>CDV15</t>
   </si>
   <si>
     <t>10015</t>
@@ -292,7 +292,7 @@
     <t>2026-09-15</t>
   </si>
   <si>
-    <t>016</t>
+    <t>CDV16</t>
   </si>
   <si>
     <t>10016</t>
@@ -304,7 +304,7 @@
     <t>2026-09-16</t>
   </si>
   <si>
-    <t>017</t>
+    <t>CDV17</t>
   </si>
   <si>
     <t>10017</t>
@@ -316,7 +316,7 @@
     <t>2026-09-17</t>
   </si>
   <si>
-    <t>018</t>
+    <t>CDV18</t>
   </si>
   <si>
     <t>10018</t>
@@ -328,7 +328,7 @@
     <t>2026-09-18</t>
   </si>
   <si>
-    <t>019</t>
+    <t>CDV19</t>
   </si>
   <si>
     <t>10019</t>
@@ -340,7 +340,7 @@
     <t>2026-09-19</t>
   </si>
   <si>
-    <t>020</t>
+    <t>CDV20</t>
   </si>
   <si>
     <t>10020</t>
@@ -352,7 +352,7 @@
     <t>2026-09-20</t>
   </si>
   <si>
-    <t>021</t>
+    <t>CDV21</t>
   </si>
   <si>
     <t>10021</t>
@@ -364,7 +364,7 @@
     <t>2026-09-21</t>
   </si>
   <si>
-    <t>022</t>
+    <t>CDV22</t>
   </si>
   <si>
     <t>10022</t>
@@ -376,7 +376,7 @@
     <t>2026-09-22</t>
   </si>
   <si>
-    <t>023</t>
+    <t>CDV23</t>
   </si>
   <si>
     <t>10023</t>
@@ -388,7 +388,7 @@
     <t>2026-09-23</t>
   </si>
   <si>
-    <t>024</t>
+    <t>CDV24</t>
   </si>
   <si>
     <t>10024</t>
@@ -400,7 +400,7 @@
     <t>2026-09-24</t>
   </si>
   <si>
-    <t>025</t>
+    <t>CDV25</t>
   </si>
   <si>
     <t>10025</t>
@@ -412,7 +412,7 @@
     <t>2026-09-25</t>
   </si>
   <si>
-    <t>026</t>
+    <t>CDV26</t>
   </si>
   <si>
     <t>10026</t>
@@ -424,7 +424,7 @@
     <t>2026-09-26</t>
   </si>
   <si>
-    <t>027</t>
+    <t>CDV27</t>
   </si>
   <si>
     <t>10027</t>
@@ -436,7 +436,7 @@
     <t>2026-09-27</t>
   </si>
   <si>
-    <t>028</t>
+    <t>CDV28</t>
   </si>
   <si>
     <t>10028</t>
@@ -448,7 +448,7 @@
     <t>2026-09-28</t>
   </si>
   <si>
-    <t>029</t>
+    <t>CDV29</t>
   </si>
   <si>
     <t>10029</t>
@@ -457,7 +457,7 @@
     <t>35261000000001002950010000000029</t>
   </si>
   <si>
-    <t>030</t>
+    <t>CDV30</t>
   </si>
   <si>
     <t>10030</t>
@@ -3026,7 +3026,7 @@
   <dimension ref="A1:I151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -7426,7 +7426,7 @@
   <dimension ref="A1:I151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -11826,7 +11826,7 @@
   <dimension ref="A1:I151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -16226,7 +16226,7 @@
   <dimension ref="A1:I151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
